--- a/artfynd/A 1385-2023 artfynd.xlsx
+++ b/artfynd/A 1385-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1385-2023 artfynd.xlsx
+++ b/artfynd/A 1385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114687630</v>
+        <v>114687615</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862002</v>
+        <v>862229</v>
       </c>
       <c r="R2" t="n">
-        <v>7495576</v>
+        <v>7495609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114687629</v>
+        <v>114687623</v>
       </c>
       <c r="B3" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861990</v>
+        <v>862193</v>
       </c>
       <c r="R3" t="n">
-        <v>7495581</v>
+        <v>7495572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,12 +874,7 @@
         <v>114687626</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,6 +966,300 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114687628</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Riukanjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>861979</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7495659</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114687630</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Riukanjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>862002</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7495576</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114687629</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96603</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skör kvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum fragilifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Riukanjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>861990</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7495581</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1385-2023 artfynd.xlsx
+++ b/artfynd/A 1385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687623</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687626</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687628</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687630</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,8 +1290,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>